--- a/projectBase-main/src/test/resources/data/registro/dataDemoblaze.xlsx
+++ b/projectBase-main/src/test/resources/data/registro/dataDemoblaze.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allumiqu\Documents\SerenityBdd-BP\projectBase-main\src\test\resources\data\registro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\SerenityBddBanP\projectBase-main\src\test\resources\data\registro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C5CCBF-ACBD-4F5E-980E-E9CA0BF7E009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="compra" sheetId="6" r:id="rId1"/>
@@ -28,8 +27,8 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" keepAlive="1" name="Consulta - datacompratelefono" description="Conexión a la consulta 'datacompratelefono' en el libro." type="5" refreshedVersion="7" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" keepAlive="1" name="Consulta - datacompratelefono" description="Conexión a la consulta 'datacompratelefono' en el libro." type="5" refreshedVersion="7" background="1" saveData="1">
     <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=datacompratelefono;Extended Properties=&quot;&quot;" command="SELECT * FROM [datacompratelefono]"/>
   </connection>
 </connections>
@@ -71,16 +70,16 @@
     <t>zip</t>
   </si>
   <si>
-    <t>Andres</t>
-  </si>
-  <si>
     <t>Llumiquinga</t>
   </si>
+  <si>
+    <t>Andy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -260,7 +259,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DatosExternos_1" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DatosExternos_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="9">
     <queryTableFields count="5">
       <queryTableField id="1" name="producto" tableColumnId="1"/>
@@ -279,13 +278,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="datacompratelefono" displayName="datacompratelefono" ref="C1:G2" tableType="queryTable" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="datacompratelefono" displayName="datacompratelefono" ref="C1:G2" tableType="queryTable" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="1" name="producto" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" uniqueName="8" name="producto1" queryTableFieldId="8" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="2" name="name" queryTableFieldId="2" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="3" name="lastname" queryTableFieldId="3" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="4" name="zip" queryTableFieldId="4" dataDxfId="0"/>
+    <tableColumn id="1" uniqueName="1" name="producto" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="8" uniqueName="8" name="producto1" queryTableFieldId="8" dataDxfId="3"/>
+    <tableColumn id="2" uniqueName="2" name="name" queryTableFieldId="2" dataDxfId="2"/>
+    <tableColumn id="3" uniqueName="3" name="lastname" queryTableFieldId="3" dataDxfId="1"/>
+    <tableColumn id="4" uniqueName="4" name="zip" queryTableFieldId="4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -553,7 +552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -603,10 +602,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="G2" s="1">
         <v>170124</v>
